--- a/AAII_Financials/Yearly/LINE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LINE_YR_FIN.xlsx
@@ -2142,7 +2142,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1176000</v>
+        <v>882000</v>
       </c>
       <c r="E57" s="3">
         <v>877000</v>
@@ -2175,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>142000</v>
+        <v>436000</v>
       </c>
       <c r="E58" s="3">
         <v>277000</v>
